--- a/data/trans_camb/Hacinamiento_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/Hacinamiento_R-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 7,55</t>
+          <t>-4,88; 6,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 11,39</t>
+          <t>-2,44; 11,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 6,02</t>
+          <t>-4,49; 5,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,44; 0,44</t>
+          <t>-9,72; 0,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 1,36</t>
+          <t>-9,96; 1,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,65; 1,89</t>
+          <t>-8,24; 1,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 1,99</t>
+          <t>-5,85; 1,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 3,97</t>
+          <t>-4,14; 4,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 2,51</t>
+          <t>-4,6; 2,68</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-78,18; 547,26</t>
+          <t>-79,8; 419,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-51,16; 646,4</t>
+          <t>-47,97; 688,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-62,94; 435,13</t>
+          <t>-68,68; 312,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 101,06</t>
+          <t>-100,0; 133,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 147,3</t>
+          <t>-100,0; 167,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-87,56; 75,11</t>
+          <t>-86,6; 64,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-82,54; 78,67</t>
+          <t>-81,07; 70,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-67,64; 144,02</t>
+          <t>-62,79; 138,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-66,8; 86,45</t>
+          <t>-66,35; 92,34</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 11,9</t>
+          <t>-1,9; 11,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 9,55</t>
+          <t>-2,21; 9,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 4,51</t>
+          <t>-5,17; 4,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,23; 4,62</t>
+          <t>-9,98; 5,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,77; 2,85</t>
+          <t>-10,77; 3,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-10,48; 3,7</t>
+          <t>-9,81; 4,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 5,56</t>
+          <t>-3,75; 6,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 4,1</t>
+          <t>-5,21; 3,81</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 2,39</t>
+          <t>-6,19; 2,36</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-46,79; 966,61</t>
+          <t>-52,11; 945,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-50,87; 697,53</t>
+          <t>-47,65; 647,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-88,52; 448,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-83,75; 109,06</t>
+          <t>-76,45; 159,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-83,27; 89,23</t>
+          <t>-82,69; 123,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-83,22; 87,35</t>
+          <t>-79,16; 122,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-50,4; 140,46</t>
+          <t>-48,55; 161,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-56,83; 110,0</t>
+          <t>-60,32; 99,27</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-70,97; 81,4</t>
+          <t>-72,5; 67,43</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 15,24</t>
+          <t>-0,87; 15,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 15,44</t>
+          <t>-3,13; 14,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 13,29</t>
+          <t>-3,37; 12,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 12,07</t>
+          <t>-2,33; 11,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 6,37</t>
+          <t>-5,24; 6,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 2,18</t>
+          <t>-6,96; 2,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 10,55</t>
+          <t>0,48; 11,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 7,8</t>
+          <t>-2,13; 7,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 4,66</t>
+          <t>-3,92; 5,15</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-23,17; 739,97</t>
+          <t>-25,16; 836,56</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-40,04; 917,26</t>
+          <t>-60,29; 669,48</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-62,02; 771,78</t>
+          <t>-59,54; 566,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-34,98; 528,58</t>
+          <t>-40,53; 519,97</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-83,08; 268,55</t>
+          <t>-80,38; 359,88</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 323,66</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-13,97; 349,89</t>
+          <t>2,33; 388,43</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-39,87; 273,84</t>
+          <t>-42,54; 273,76</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-62,91; 166,16</t>
+          <t>-63,25; 202,24</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,13; 12,32</t>
+          <t>2,26; 12,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 8,1</t>
+          <t>-0,91; 7,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 2,73</t>
+          <t>-4,39; 2,89</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,03; 10,09</t>
+          <t>0,17; 9,72</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 6,49</t>
+          <t>-1,96; 6,28</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 9,39</t>
+          <t>-0,5; 9,5</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,95; 9,44</t>
+          <t>2,15; 9,13</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 5,73</t>
+          <t>-0,22; 5,66</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 4,95</t>
+          <t>-1,27; 5,05</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>24,23; 454,75</t>
+          <t>24,21; 448,71</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-20,02; 290,26</t>
+          <t>-21,84; 283,01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-67,95; 108,05</t>
+          <t>-66,39; 118,85</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-8,63; 321,64</t>
+          <t>-3,19; 323,41</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-32,51; 228,18</t>
+          <t>-31,16; 219,97</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-15,95; 329,18</t>
+          <t>-9,79; 297,05</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,12; 260,16</t>
+          <t>26,58; 254,55</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 165,17</t>
+          <t>-4,3; 170,12</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-20,83; 150,75</t>
+          <t>-22,36; 151,09</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-11,78; 5,04</t>
+          <t>-10,64; 5,12</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-10,66; 6,12</t>
+          <t>-10,68; 5,55</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-10,42; 6,16</t>
+          <t>-11,29; 4,8</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-10,18; 7,79</t>
+          <t>-9,22; 8,14</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,9; 6,9</t>
+          <t>-9,8; 7,25</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-12,88; 2,66</t>
+          <t>-12,33; 2,4</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 3,08</t>
+          <t>-7,83; 4,64</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 3,86</t>
+          <t>-8,23; 3,48</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-9,04; 2,19</t>
+          <t>-8,98; 2,32</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-63,97; 65,95</t>
+          <t>-60,95; 65,25</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-56,96; 79,45</t>
+          <t>-56,21; 71,0</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-56,6; 79,03</t>
+          <t>-59,49; 54,49</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-49,54; 76,8</t>
+          <t>-47,36; 71,48</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-51,35; 64,38</t>
+          <t>-50,25; 72,77</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-63,44; 24,51</t>
+          <t>-61,44; 24,97</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-47,02; 26,05</t>
+          <t>-47,31; 39,94</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-42,55; 35,23</t>
+          <t>-46,27; 32,56</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-51,37; 22,12</t>
+          <t>-50,73; 21,06</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-6,88; 11,72</t>
+          <t>-6,5; 12,58</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-10,95; 3,74</t>
+          <t>-10,41; 4,57</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-12,31; 3,02</t>
+          <t>-11,49; 3,69</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-7,58; 8,68</t>
+          <t>-8,19; 9,19</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-13,91; -0,07</t>
+          <t>-14,63; -0,4</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 14,68</t>
+          <t>-4,77; 13,9</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 8,3</t>
+          <t>-4,37; 8,25</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-10,75; -0,43</t>
+          <t>-11,05; -0,92</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 6,7</t>
+          <t>-5,9; 6,34</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-51,18; 174,01</t>
+          <t>-47,78; 191,33</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-80,61; 63,35</t>
+          <t>-75,87; 82,31</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-79,29; 61,88</t>
+          <t>-77,89; 68,87</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-51,46; 125,75</t>
+          <t>-54,22; 136,21</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-90,92; 12,08</t>
+          <t>-91,55; 13,02</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-36,7; 195,4</t>
+          <t>-31,97; 204,57</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-31,46; 102,85</t>
+          <t>-32,81; 101,84</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-77,24; -0,08</t>
+          <t>-78,64; -1,8</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-42,6; 84,3</t>
+          <t>-44,07; 76,26</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,7; 6,32</t>
+          <t>0,76; 6,56</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 4,47</t>
+          <t>-0,53; 5,09</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 1,61</t>
+          <t>-2,96; 1,68</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 3,87</t>
+          <t>-1,42; 4,04</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 1,26</t>
+          <t>-4,08; 1,12</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 2,65</t>
+          <t>-2,77; 2,71</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,26; 4,3</t>
+          <t>0,44; 4,36</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 2,04</t>
+          <t>-1,62; 2,18</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 1,59</t>
+          <t>-2,15; 1,59</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>5,56; 116,06</t>
+          <t>9,94; 123,82</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-9,09; 82,19</t>
+          <t>-7,73; 92,94</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-42,79; 31,02</t>
+          <t>-38,05; 32,03</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-18,24; 60,24</t>
+          <t>-15,94; 61,19</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-41,86; 21,04</t>
+          <t>-43,09; 17,46</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-29,1; 38,93</t>
+          <t>-29,71; 40,09</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,75; 65,08</t>
+          <t>4,13; 66,66</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-20,68; 32,59</t>
+          <t>-20,0; 34,41</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-25,13; 25,71</t>
+          <t>-27,06; 25,18</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/Hacinamiento_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/Hacinamiento_R-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 6,97</t>
+          <t>-5,17; 7,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 11,27</t>
+          <t>-2,73; 11,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 5,4</t>
+          <t>-4,48; 6,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,72; 0,96</t>
+          <t>-9,84; 0,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,96; 1,29</t>
+          <t>-9,71; 1,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,24; 1,41</t>
+          <t>-8,7; 1,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 1,87</t>
+          <t>-5,95; 2,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 4,23</t>
+          <t>-4,01; 4,17</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 2,68</t>
+          <t>-4,87; 2,49</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-79,8; 419,89</t>
+          <t>-85,53; 406,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-47,97; 688,27</t>
+          <t>-53,29; 538,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-68,68; 312,14</t>
+          <t>-65,34; 376,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 133,67</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 167,52</t>
+          <t>-100,0; 193,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-86,6; 64,49</t>
+          <t>-87,73; 100,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-81,07; 70,85</t>
+          <t>-79,59; 92,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-62,79; 138,05</t>
+          <t>-66,12; 139,11</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-66,35; 92,34</t>
+          <t>-64,83; 87,59</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 11,78</t>
+          <t>-2,07; 11,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 9,04</t>
+          <t>-2,3; 9,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 4,58</t>
+          <t>-5,67; 4,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,98; 5,24</t>
+          <t>-9,86; 4,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,77; 3,25</t>
+          <t>-11,37; 3,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,81; 4,13</t>
+          <t>-9,94; 3,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 6,21</t>
+          <t>-3,53; 6,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 3,81</t>
+          <t>-4,5; 4,18</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 2,36</t>
+          <t>-6,25; 2,38</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-52,11; 945,36</t>
+          <t>-49,11; 1026,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-47,65; 647,23</t>
+          <t>-55,29; 760,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-88,52; 448,43</t>
+          <t>-84,76; 410,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-76,45; 159,35</t>
+          <t>-76,25; 108,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-82,69; 123,17</t>
+          <t>-83,71; 109,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-79,16; 122,8</t>
+          <t>-80,39; 107,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-48,55; 161,26</t>
+          <t>-45,92; 165,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-60,32; 99,27</t>
+          <t>-56,55; 123,0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-72,5; 67,43</t>
+          <t>-71,44; 77,4</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 15,18</t>
+          <t>-1,64; 14,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 14,97</t>
+          <t>-2,97; 13,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 12,59</t>
+          <t>-3,06; 12,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 11,49</t>
+          <t>-2,06; 12,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 6,24</t>
+          <t>-5,39; 6,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 2,46</t>
+          <t>-7,37; 2,23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 11,0</t>
+          <t>0,41; 11,5</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 7,65</t>
+          <t>-2,39; 7,83</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 5,15</t>
+          <t>-3,54; 5,1</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-25,16; 836,56</t>
+          <t>-30,68; 950,58</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-60,29; 669,48</t>
+          <t>-62,48; 784,79</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-59,54; 566,26</t>
+          <t>-54,1; 752,67</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-40,53; 519,97</t>
+          <t>-45,07; 490,65</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-80,38; 359,88</t>
+          <t>-84,38; 348,26</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 323,66</t>
+          <t>-100,0; 191,68</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,33; 388,43</t>
+          <t>2,77; 418,66</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-42,54; 273,76</t>
+          <t>-39,02; 303,47</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-63,25; 202,24</t>
+          <t>-57,2; 208,68</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,26; 12,44</t>
+          <t>1,83; 12,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 7,91</t>
+          <t>-1,11; 7,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 2,89</t>
+          <t>-4,53; 2,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,17; 9,72</t>
+          <t>-0,15; 9,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 6,28</t>
+          <t>-2,13; 6,72</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 9,5</t>
+          <t>-0,66; 9,7</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,15; 9,13</t>
+          <t>2,28; 9,29</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 5,66</t>
+          <t>-0,33; 6,05</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 5,05</t>
+          <t>-1,49; 5,08</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>24,21; 448,71</t>
+          <t>16,89; 466,3</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-21,84; 283,01</t>
+          <t>-20,28; 299,24</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-66,39; 118,85</t>
+          <t>-64,33; 111,18</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 323,41</t>
+          <t>-7,89; 317,98</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-31,16; 219,97</t>
+          <t>-32,46; 230,5</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-9,79; 297,05</t>
+          <t>-14,12; 308,58</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,58; 254,55</t>
+          <t>34,6; 272,98</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 170,12</t>
+          <t>-5,39; 182,98</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-22,36; 151,09</t>
+          <t>-23,48; 147,95</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-10,64; 5,12</t>
+          <t>-11,75; 5,55</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-10,68; 5,55</t>
+          <t>-9,97; 7,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-11,29; 4,8</t>
+          <t>-10,79; 5,48</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-9,22; 8,14</t>
+          <t>-9,2; 8,07</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,8; 7,25</t>
+          <t>-11,35; 6,23</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-12,33; 2,4</t>
+          <t>-12,51; 2,77</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 4,64</t>
+          <t>-8,19; 4,05</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 3,48</t>
+          <t>-8,1; 3,97</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 2,32</t>
+          <t>-9,84; 1,84</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-60,95; 65,25</t>
+          <t>-64,01; 67,23</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-56,21; 71,0</t>
+          <t>-57,22; 96,04</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-59,49; 54,49</t>
+          <t>-56,99; 76,65</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-47,36; 71,48</t>
+          <t>-49,24; 81,73</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-50,25; 72,77</t>
+          <t>-54,67; 56,81</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-61,44; 24,97</t>
+          <t>-62,54; 30,87</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-47,31; 39,94</t>
+          <t>-47,37; 36,02</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-46,27; 32,56</t>
+          <t>-43,72; 35,44</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-50,73; 21,06</t>
+          <t>-51,73; 17,58</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 12,58</t>
+          <t>-6,33; 12,13</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-10,41; 4,57</t>
+          <t>-11,31; 5,05</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-11,49; 3,69</t>
+          <t>-11,38; 3,45</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 9,19</t>
+          <t>-8,01; 9,69</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-14,63; -0,4</t>
+          <t>-13,97; -0,2</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 13,9</t>
+          <t>-4,58; 14,88</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 8,25</t>
+          <t>-4,74; 7,73</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-11,05; -0,92</t>
+          <t>-10,81; -0,31</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 6,34</t>
+          <t>-5,13; 7,62</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-47,78; 191,33</t>
+          <t>-51,98; 188,23</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-75,87; 82,31</t>
+          <t>-76,75; 96,48</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-77,89; 68,87</t>
+          <t>-75,44; 67,35</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-54,22; 136,21</t>
+          <t>-54,41; 151,02</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-91,55; 13,02</t>
+          <t>-92,01; 27,03</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-31,97; 204,57</t>
+          <t>-37,3; 203,27</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-32,81; 101,84</t>
+          <t>-34,75; 91,89</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-78,64; -1,8</t>
+          <t>-78,23; -2,44</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-44,07; 76,26</t>
+          <t>-39,64; 90,84</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,76; 6,56</t>
+          <t>0,8; 6,64</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 5,09</t>
+          <t>-0,93; 4,64</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 1,68</t>
+          <t>-3,16; 1,86</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 4,04</t>
+          <t>-1,31; 4,25</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 1,12</t>
+          <t>-3,93; 1,08</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 2,71</t>
+          <t>-2,51; 2,89</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,36</t>
+          <t>0,36; 4,36</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 2,18</t>
+          <t>-1,75; 1,88</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 1,59</t>
+          <t>-1,98; 1,61</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>9,94; 123,82</t>
+          <t>9,3; 119,96</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 92,94</t>
+          <t>-11,71; 86,8</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-38,05; 32,03</t>
+          <t>-39,71; 32,41</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-15,94; 61,19</t>
+          <t>-15,15; 61,84</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-43,09; 17,46</t>
+          <t>-42,5; 16,09</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-29,71; 40,09</t>
+          <t>-26,3; 44,37</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,13; 66,66</t>
+          <t>4,12; 67,44</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-20,0; 34,41</t>
+          <t>-21,63; 28,9</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-27,06; 25,18</t>
+          <t>-25,03; 25,09</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/Hacinamiento_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/Hacinamiento_R-Clase-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-3,88</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-3,75</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-2,87</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,54</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>3,73</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,84</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-3,88</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-3,75</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-2,61</t>
+          <t>1,02</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,98</t>
+          <t>-0,99</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 7,08</t>
+          <t>-9,44; 0,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 11,02</t>
+          <t>-8,82; 1,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 6,13</t>
+          <t>-9,08; 1,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,84; 0,68</t>
+          <t>-4,86; 7,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,71; 1,36</t>
+          <t>-2,81; 11,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,7; 1,93</t>
+          <t>-4,24; 6,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 2,15</t>
+          <t>-5,71; 1,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 4,17</t>
+          <t>-4,62; 3,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 2,49</t>
+          <t>-4,81; 2,48</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-66,74%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-64,47%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-49,38%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>12,45%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>85,91%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>19,35%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-66,74%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-64,47%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-44,98%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-19,43%</t>
+          <t>-19,61%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-85,53; 406,65</t>
+          <t>-100,0; 101,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-53,29; 538,68</t>
+          <t>-100,0; 147,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-65,34; 376,16</t>
+          <t>-88,93; 74,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-78,18; 547,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 193,74</t>
+          <t>-51,16; 646,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-87,73; 100,04</t>
+          <t>-62,6; 427,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-79,59; 92,28</t>
+          <t>-82,54; 78,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-66,12; 139,11</t>
+          <t>-67,64; 144,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-64,83; 87,59</t>
+          <t>-65,13; 92,35</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-2,3</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-3,57</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-2,79</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>4,06</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>3,27</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,53</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-2,3</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-3,57</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-2,9</t>
+          <t>-0,09</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-1,69</t>
+          <t>-1,45</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 11,24</t>
+          <t>-11,23; 4,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 9,59</t>
+          <t>-10,77; 2,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 4,09</t>
+          <t>-10,56; 3,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,86; 4,51</t>
+          <t>-2,24; 11,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,37; 3,05</t>
+          <t>-2,3; 9,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,94; 3,6</t>
+          <t>-5,15; 5,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 6,37</t>
+          <t>-4,21; 5,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 4,18</t>
+          <t>-4,79; 4,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 2,38</t>
+          <t>-6,14; 2,8</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-26,97%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-41,81%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-32,65%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>105,29%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>84,62%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-13,73%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-26,97%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-41,81%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-33,95%</t>
+          <t>-2,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-27,36%</t>
+          <t>-23,44%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-49,11; 1026,46</t>
+          <t>-83,75; 109,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-55,29; 760,18</t>
+          <t>-83,27; 89,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-84,76; 410,64</t>
+          <t>-82,57; 92,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-76,25; 108,98</t>
+          <t>-46,79; 966,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-83,71; 109,18</t>
+          <t>-50,87; 697,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-80,39; 107,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-45,92; 165,51</t>
+          <t>-50,4; 140,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-56,55; 123,0</t>
+          <t>-56,83; 110,0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-71,44; 77,4</t>
+          <t>-69,21; 89,31</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>4,32</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,15</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-2,61</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>6,79</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>5,38</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>4,09</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4,32</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,15</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-2,5</t>
+          <t>3,22</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,38</t>
+          <t>0,14</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 14,87</t>
+          <t>-1,53; 12,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 13,84</t>
+          <t>-5,12; 6,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 12,51</t>
+          <t>-7,69; 1,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 12,16</t>
+          <t>-0,44; 15,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 6,14</t>
+          <t>-1,89; 15,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 2,23</t>
+          <t>-4,21; 11,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,41; 11,5</t>
+          <t>-0,24; 10,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 7,83</t>
+          <t>-2,51; 7,8</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 5,1</t>
+          <t>-4,31; 4,29</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>93,37%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3,23%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-56,49%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>138,73%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>109,97%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>83,52%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>93,37%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>3,23%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-54,11%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-30,68; 950,58</t>
+          <t>-34,98; 528,58</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-62,48; 784,79</t>
+          <t>-83,08; 268,55</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-54,1; 752,67</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-45,07; 490,65</t>
+          <t>-23,17; 739,97</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-84,38; 348,26</t>
+          <t>-40,04; 917,26</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 191,68</t>
+          <t>-64,25; 701,29</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,77; 418,66</t>
+          <t>-13,97; 349,89</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-39,02; 303,47</t>
+          <t>-39,87; 273,84</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-57,2; 208,68</t>
+          <t>-66,13; 154,34</t>
         </is>
       </c>
     </row>
@@ -1272,47 +1272,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4,78</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2,13</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4,16</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>7,06</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>3,29</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,8</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4,78</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>-0,21</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>5,84</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2,71</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>2,13</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4,34</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>5,84</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2,71</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1,78</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,83; 12,8</t>
+          <t>0,03; 10,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 7,66</t>
+          <t>-2,19; 6,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 2,68</t>
+          <t>-0,57; 9,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 9,73</t>
+          <t>2,13; 12,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 6,72</t>
+          <t>-0,96; 8,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 9,7</t>
+          <t>-3,81; 3,4</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,28; 9,29</t>
+          <t>1,95; 9,44</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 6,05</t>
+          <t>-0,4; 5,73</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 5,08</t>
+          <t>-0,99; 5,27</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>96,97%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>43,24%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>84,43%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>152,14%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>70,99%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-17,2%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>96,97%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>43,24%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>-4,52%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>44,46%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>16,89; 466,3</t>
+          <t>-8,63; 321,64</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-20,28; 299,24</t>
+          <t>-32,51; 228,18</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-64,33; 111,18</t>
+          <t>-14,56; 325,95</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 317,98</t>
+          <t>24,23; 454,75</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-32,46; 230,5</t>
+          <t>-20,02; 290,26</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-14,12; 308,58</t>
+          <t>-59,65; 133,67</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,6; 272,98</t>
+          <t>29,12; 260,16</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 182,98</t>
+          <t>-6,82; 165,17</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-23,48; 147,95</t>
+          <t>-16,9; 156,61</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-1,02</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-1,58</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-5,63</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-2,94</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-1,87</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-2,06</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-1,02</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-1,58</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-4,57</t>
+          <t>-1,82</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-3,45</t>
+          <t>-3,93</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-11,75; 5,55</t>
+          <t>-10,18; 7,79</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-9,97; 7,0</t>
+          <t>-9,9; 6,9</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-10,79; 5,48</t>
+          <t>-14,09; 0,98</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-9,2; 8,07</t>
+          <t>-11,78; 5,04</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-11,35; 6,23</t>
+          <t>-10,66; 6,12</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-12,51; 2,77</t>
+          <t>-10,33; 6,27</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 4,05</t>
+          <t>-8,2; 3,08</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-8,1; 3,97</t>
+          <t>-7,25; 3,86</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-9,84; 1,84</t>
+          <t>-9,67; 1,74</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-6,6%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-10,2%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-36,45%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-22,49%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-14,34%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-15,8%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-6,6%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-10,2%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-29,59%</t>
+          <t>-13,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-24,0%</t>
+          <t>-27,33%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-64,01; 67,23</t>
+          <t>-49,54; 76,8</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-57,22; 96,04</t>
+          <t>-51,35; 64,38</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-56,99; 76,65</t>
+          <t>-67,07; 12,86</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-49,24; 81,73</t>
+          <t>-63,97; 65,95</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-54,67; 56,81</t>
+          <t>-56,96; 79,45</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-62,54; 30,87</t>
+          <t>-54,28; 81,64</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-47,37; 36,02</t>
+          <t>-47,02; 26,05</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-43,72; 35,44</t>
+          <t>-42,55; 35,23</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-51,73; 17,58</t>
+          <t>-53,16; 17,62</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>0,72</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-6,87</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>4,18</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>2,53</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>-3,9</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-4,12</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>0,72</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-6,87</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,68</t>
+          <t>-3,87</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,38</t>
+          <t>0,1</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 12,13</t>
+          <t>-7,58; 8,68</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-11,31; 5,05</t>
+          <t>-13,91; -0,07</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-11,38; 3,45</t>
+          <t>-5,12; 14,13</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-8,01; 9,69</t>
+          <t>-6,88; 11,72</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-13,97; -0,2</t>
+          <t>-10,95; 3,74</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 14,88</t>
+          <t>-11,88; 3,75</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 7,73</t>
+          <t>-3,98; 8,3</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-10,81; -0,31</t>
+          <t>-10,75; -0,43</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 7,62</t>
+          <t>-6,02; 6,58</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>6,51%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-62,39%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>38,01%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>23,61%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>-36,41%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-38,5%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>6,51%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-62,39%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>-36,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-51,98; 188,23</t>
+          <t>-51,46; 125,75</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-76,75; 96,48</t>
+          <t>-90,92; 12,08</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-75,44; 67,35</t>
+          <t>-42,67; 187,35</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-54,41; 151,02</t>
+          <t>-51,18; 174,01</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-92,01; 27,03</t>
+          <t>-80,61; 63,35</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-37,3; 203,27</t>
+          <t>-78,92; 69,29</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-34,75; 91,89</t>
+          <t>-31,46; 102,85</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-78,23; -2,44</t>
+          <t>-77,24; -0,08</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-39,64; 90,84</t>
+          <t>-43,68; 84,44</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>1,22</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-1,35</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>-0,24</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>3,59</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>1,97</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-0,61</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>1,22</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-1,35</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>-0,21</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-0,21</t>
+          <t>-0,2</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,8; 6,64</t>
+          <t>-1,77; 3,87</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 4,64</t>
+          <t>-3,89; 1,26</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 1,86</t>
+          <t>-2,94; 2,37</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 4,25</t>
+          <t>0,7; 6,32</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 1,08</t>
+          <t>-0,73; 4,47</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 2,89</t>
+          <t>-2,88; 2,18</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,36; 4,36</t>
+          <t>0,26; 4,3</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 1,88</t>
+          <t>-1,7; 2,04</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 1,61</t>
+          <t>-1,99; 1,64</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>15,26%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-16,9%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>-2,97%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>54,7%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>30,03%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-9,26%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>15,26%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-16,9%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>-3,12%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-2,86%</t>
+          <t>-2,76%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>9,3; 119,96</t>
+          <t>-18,24; 60,24</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-11,71; 86,8</t>
+          <t>-41,86; 21,04</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-39,71; 32,41</t>
+          <t>-31,86; 35,96</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-15,15; 61,84</t>
+          <t>5,56; 116,06</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-42,5; 16,09</t>
+          <t>-9,09; 82,19</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-26,3; 44,37</t>
+          <t>-36,6; 41,17</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,12; 67,44</t>
+          <t>2,75; 65,08</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-21,63; 28,9</t>
+          <t>-20,68; 32,59</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-25,03; 25,09</t>
+          <t>-24,49; 26,08</t>
         </is>
       </c>
     </row>
